--- a/technology_surveys/016_nanobubble_technology_survey--technology_surveys.xlsx
+++ b/technology_surveys/016_nanobubble_technology_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,138 +515,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form Header</t>
+          <t>What is your current level of awareness about nanobubble technology?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>nanobubble_technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>List the nanobubble technologies you are aware of</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_header_2</t>
+          <t>use_case</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Form Header 2</t>
+          <t>How do you currently use nanobubble technology?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>use_cases</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Use cases</t>
+          <t>What are the benefits you get from using nanobubble technology?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>benefits</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Benefits</t>
+          <t>What are the challenges you face when using nanobubble technology?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>goals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>What are your goals for nanobubble technology?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,19 +658,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter the number of nanobubble technologies you are aware of</t>
-        </is>
-      </c>
+          <t>Which nanobubble technology are you most interested in?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -685,19 +681,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>preference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you are most familiar with</t>
-        </is>
-      </c>
+          <t>What is your preferred nanobubble technology?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -712,19 +704,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>challenges_use</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you are most interested in</t>
-        </is>
-      </c>
+          <t>What are your challenges when using nanobubble technology?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -739,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>future_goals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you most often use</t>
-        </is>
-      </c>
+          <t>What are your future goals for nanobubble technology?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -761,399 +745,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you would like to see developed</t>
-        </is>
-      </c>
+          <t>Form Footer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you have most experience with</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you would like to see in the future</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you are most likely to recommend</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you would like to learn more about</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you would use</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you would recommend</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter the nanobubble technology you are familiar with</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>awareness_challenges</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Challenges</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter the challenges you face when using nanobubble technology</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter the challenges you face when using nanobubble technology</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Enter the challenges you face when developing or implementing nanobubble technology</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>awareness</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter prophets related to nanobubbles technology</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>goals</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>What are your goals for nanobubble technology</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>benefits_goals</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Benefits_goals</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>What benefits do you get when using nanobubble technology</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_footer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Form Footer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1170,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1220,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1237,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1254,199 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>use_cases_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'label':_'awareness_goals'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'label': 'Awareness_goals'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>use_cases_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_reduction'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'label': 'Cost_reduction'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>use_cases_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'productive_process'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Productive_process'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>use_cases_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'easy_to_adopt'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Easy_to_adopt'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'high_quality_data'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'High_quality_data'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'increased_accuracy'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'Increased_accuracy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_'limited_access'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': 'Limited_access'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'high_cost'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'High_cost'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
